--- a/Mediciones/Exploracion/Serpiente/RUN_5_5M_Serp_6NO.xlsx
+++ b/Mediciones/Exploracion/Serpiente/RUN_5_5M_Serp_6NO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Henry\Desktop\Exploracion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\Exploracion\Serpiente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA2B8E0-B5EB-4090-87A1-ABD58C535714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3071710B-99F8-4A68-97B6-5750E260CE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -77,9 +77,6 @@
     <t>2026-07-17T16:00:30</t>
   </si>
   <si>
-    <t>Centro de gravedad</t>
-  </si>
-  <si>
     <t>2026-07-17T16:00:33</t>
   </si>
   <si>
@@ -567,6 +564,9 @@
   </si>
   <si>
     <t>}</t>
+  </si>
+  <si>
+    <t>Exploracion frontera</t>
   </si>
 </sst>
 </file>
@@ -922,87 +922,87 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
@@ -1032,397 +1032,397 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2">
         <v>1.4194065929311481E-2</v>
@@ -1538,13 +1538,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3">
         <v>1.426109688941552E-2</v>
@@ -1579,13 +1579,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4">
         <v>1.426109688941552E-2</v>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5">
         <v>1.426109688941552E-2</v>
@@ -1661,13 +1661,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6">
         <v>1.426109688941552E-2</v>
@@ -1702,13 +1702,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>1.426109688941552E-2</v>
@@ -1743,13 +1743,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>1.426109688941552E-2</v>
@@ -1784,13 +1784,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D9">
         <v>1.426109688941552E-2</v>
@@ -1825,13 +1825,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D10">
         <v>1.426109688941552E-2</v>
@@ -1866,13 +1866,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11">
         <v>1.426109688941552E-2</v>
@@ -1907,13 +1907,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12">
         <v>1.426109688941552E-2</v>
@@ -1948,13 +1948,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D13">
         <v>1.426109688941552E-2</v>
@@ -1989,13 +1989,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14">
         <v>1.426109688941552E-2</v>
@@ -2030,13 +2030,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D15">
         <v>1.783419895110866E-2</v>
@@ -2071,13 +2071,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16">
         <v>1.783419895110866E-2</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17">
         <v>1.783419895110866E-2</v>
@@ -2153,13 +2153,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18">
         <v>1.783419895110866E-2</v>
@@ -2194,13 +2194,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19">
         <v>1.783419895110866E-2</v>
@@ -2235,13 +2235,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20">
         <v>1.783419895110866E-2</v>
@@ -2276,13 +2276,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21">
         <v>1.783419895110866E-2</v>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22">
         <v>1.8047963128105929E-2</v>
@@ -2358,13 +2358,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D23">
         <v>1.8047963128105929E-2</v>
@@ -2399,13 +2399,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24">
         <v>1.8047963128105929E-2</v>
@@ -2440,13 +2440,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25">
         <v>1.8047963128105929E-2</v>
@@ -2481,13 +2481,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26">
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D26">
         <v>1.8047963128105929E-2</v>
@@ -2522,13 +2522,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27">
         <v>1.8047963128105929E-2</v>
@@ -2563,13 +2563,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28">
         <v>1.8047963128105929E-2</v>
@@ -2604,13 +2604,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29">
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D29">
         <v>1.8047963128105929E-2</v>
@@ -2645,13 +2645,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D30">
         <v>2.0260099696330629E-2</v>
@@ -2686,13 +2686,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31">
         <v>2.0260099696330629E-2</v>
@@ -2727,13 +2727,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B32">
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D32">
         <v>2.0260099696330629E-2</v>
@@ -2768,13 +2768,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D33">
         <v>2.0260099696330629E-2</v>
@@ -2809,13 +2809,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D34">
         <v>2.0260099696330629E-2</v>
@@ -2850,13 +2850,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35">
         <v>2.0260099696330629E-2</v>
@@ -2891,13 +2891,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36">
         <v>2.0260099696330629E-2</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37">
         <v>2.0260099696330629E-2</v>
@@ -2973,13 +2973,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38">
         <v>2.0260099696330629E-2</v>
@@ -3014,13 +3014,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39">
         <v>2.0260099696330629E-2</v>
@@ -3055,13 +3055,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40">
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40">
         <v>2.0260099696330629E-2</v>
@@ -3096,13 +3096,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D41">
         <v>2.0260099696330629E-2</v>
@@ -3137,13 +3137,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D42">
         <v>2.0260099696330629E-2</v>
@@ -3178,13 +3178,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43">
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D43">
         <v>2.0260099696330629E-2</v>
@@ -3219,13 +3219,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44">
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D44">
         <v>2.0260099696330629E-2</v>
@@ -3260,13 +3260,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45">
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D45">
         <v>2.2219670162115311E-2</v>
@@ -3301,13 +3301,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46">
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D46">
         <v>2.2219670162115311E-2</v>
@@ -3342,13 +3342,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47">
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D47">
         <v>2.2219670162115311E-2</v>
@@ -3383,13 +3383,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D48">
         <v>2.2219670162115311E-2</v>
@@ -3424,13 +3424,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D49">
         <v>2.2219670162115311E-2</v>
@@ -3465,13 +3465,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D50">
         <v>2.6866933251827679E-2</v>
@@ -3506,13 +3506,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51">
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D51">
         <v>2.6866933251827679E-2</v>
@@ -3547,13 +3547,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D52">
         <v>8.8690570834870683E-2</v>
@@ -3588,13 +3588,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B53">
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D53">
         <v>0.38856612532026191</v>
@@ -3629,13 +3629,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B54">
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D54">
         <v>0.69243282076881107</v>
@@ -3670,13 +3670,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55">
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D55">
         <v>0.87506190793440974</v>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56">
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56">
         <v>0.87506190793440974</v>
@@ -3752,13 +3752,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57">
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D57">
         <v>0.96747545722753303</v>
@@ -3793,13 +3793,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58">
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D58">
         <v>0.96747545722753303</v>
@@ -3834,13 +3834,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59">
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D59">
         <v>0.96747545722753303</v>
@@ -3875,13 +3875,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B60">
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D60">
         <v>0.96747545722753303</v>
@@ -3916,13 +3916,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B61">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D61">
         <v>0.96747545722753303</v>
@@ -3957,13 +3957,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62">
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D62">
         <v>0.96747545722753303</v>
@@ -3998,13 +3998,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B63">
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63">
         <v>0.96747545722753303</v>
@@ -4039,13 +4039,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64">
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D64">
         <v>0.96747545722753303</v>
@@ -4080,13 +4080,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65">
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D65">
         <v>0.98717346782476623</v>
@@ -4121,13 +4121,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66">
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D66">
         <v>0.98717346782476623</v>
@@ -4162,13 +4162,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67">
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D67">
         <v>0.98717346782476623</v>
@@ -4203,13 +4203,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68">
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D68">
         <v>0.98717346782476623</v>
@@ -4244,13 +4244,13 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B69">
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D69">
         <v>0.98717346782476623</v>
@@ -4285,13 +4285,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B70">
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D70">
         <v>0.98717346782476623</v>
@@ -4326,13 +4326,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B71">
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D71">
         <v>0.98717346782476623</v>
@@ -4367,13 +4367,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B72">
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D72">
         <v>0.98717346782476623</v>
@@ -4408,13 +4408,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B73">
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D73">
         <v>0.98717346782476623</v>
@@ -4449,13 +4449,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74">
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D74">
         <v>0.98717346782476623</v>
@@ -4490,13 +4490,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75">
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D75">
         <v>0.98717346782476623</v>
@@ -4531,13 +4531,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76">
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D76">
         <v>0.98717346782476623</v>
@@ -4572,13 +4572,13 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77">
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D77">
         <v>0.98717346782476623</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B78">
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D78">
         <v>0.98717346782476623</v>
@@ -4654,13 +4654,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B79">
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D79">
         <v>0.98717346782476623</v>
@@ -4695,13 +4695,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B80">
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D80">
         <v>0.98717346782476623</v>
@@ -4736,13 +4736,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B81">
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D81">
         <v>0.98717346782476623</v>
@@ -4777,13 +4777,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B82">
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D82">
         <v>0.98717346782476623</v>
@@ -4818,13 +4818,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B83">
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D83">
         <v>0.98717346782476623</v>
@@ -4859,13 +4859,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B84">
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D84">
         <v>0.98717346782476623</v>
@@ -4900,13 +4900,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B85">
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D85">
         <v>0.98717346782476623</v>
@@ -4941,13 +4941,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D86">
         <v>0.98717346782476623</v>
@@ -4982,13 +4982,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B87">
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D87">
         <v>0.98717346782476623</v>
@@ -5023,13 +5023,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B88">
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D88">
         <v>0.98717346782476623</v>
@@ -5064,13 +5064,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B89">
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D89">
         <v>0.98717346782476623</v>
@@ -5105,13 +5105,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B90">
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D90">
         <v>0.98717346782476623</v>
@@ -5146,13 +5146,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B91">
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D91">
         <v>0.98717346782476623</v>
@@ -5187,13 +5187,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B92">
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D92">
         <v>0.98717346782476623</v>
@@ -5228,13 +5228,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B93">
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D93">
         <v>0.98717346782476623</v>
@@ -5269,13 +5269,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B94">
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D94">
         <v>0.98717346782476623</v>
@@ -5310,13 +5310,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B95">
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D95">
         <v>0.98717346782476623</v>
@@ -5351,13 +5351,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B96">
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D96">
         <v>0.98717346782476623</v>
@@ -5392,13 +5392,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B97">
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D97">
         <v>0.98717346782476623</v>
@@ -5433,13 +5433,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B98">
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D98">
         <v>0.98717346782476623</v>
@@ -5474,13 +5474,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B99">
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D99">
         <v>0.98717346782476623</v>
@@ -5515,13 +5515,13 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B100">
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D100">
         <v>0.98717346782476623</v>
@@ -5556,13 +5556,13 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B101">
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D101">
         <v>0.98717346782476623</v>
@@ -5597,13 +5597,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B102">
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D102">
         <v>0.98717346782476623</v>
@@ -5638,13 +5638,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B103">
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D103">
         <v>0.98717346782476623</v>
@@ -5679,13 +5679,13 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B104">
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D104">
         <v>0.98717346782476623</v>
@@ -5720,13 +5720,13 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B105">
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D105">
         <v>0.98717346782476623</v>
@@ -5761,13 +5761,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B106">
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D106">
         <v>0.98717346782476623</v>
@@ -5802,13 +5802,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B107">
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D107">
         <v>0.98717346782476623</v>
@@ -5843,13 +5843,13 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B108">
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D108">
         <v>0.98717346782476623</v>
@@ -5884,13 +5884,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B109">
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D109">
         <v>0.98717346782476623</v>
@@ -5925,13 +5925,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B110">
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D110">
         <v>0.98717346782476623</v>
@@ -5966,13 +5966,13 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B111">
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D111">
         <v>0.98717346782476623</v>
@@ -6007,13 +6007,13 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B112">
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D112">
         <v>0.98717346782476623</v>
@@ -6048,13 +6048,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B113">
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D113">
         <v>0.98717346782476623</v>
@@ -6089,13 +6089,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114">
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D114">
         <v>0.98717346782476623</v>
@@ -6130,13 +6130,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B115">
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D115">
         <v>0.98717346782476623</v>
@@ -6171,13 +6171,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B116">
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D116">
         <v>0.98717346782476623</v>
@@ -6212,13 +6212,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B117">
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D117">
         <v>0.98717346782476623</v>
@@ -6253,13 +6253,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B118">
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D118">
         <v>0.98717346782476623</v>
@@ -6294,13 +6294,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B119">
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D119">
         <v>0.98717346782476623</v>
@@ -6335,13 +6335,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B120">
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D120">
         <v>0.98717346782476623</v>
@@ -6376,13 +6376,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B121">
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D121">
         <v>0.98717346782476623</v>
@@ -6432,25 +6432,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>68</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>70</v>
-      </c>
-      <c r="G1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -8539,10 +8539,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s">
         <v>72</v>
-      </c>
-      <c r="B1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -8602,13 +8602,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -9596,16 +9596,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" t="s">
-        <v>77</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -11990,16 +11990,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" t="s">
         <v>78</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>79</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -12017,15 +12017,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -12033,7 +12033,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3">
         <v>1.9</v>
@@ -12041,7 +12041,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5">
         <v>1.2</v>
@@ -12060,12 +12060,12 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7">
         <v>120</v>
@@ -12097,7 +12097,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B11">
         <v>0.98717299999999997</v>
@@ -12105,7 +12105,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <v>1.505190699995729</v>
@@ -12113,7 +12113,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13">
         <v>106.53359870001439</v>
@@ -12121,7 +12121,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B14">
         <v>1.4128788648491651E-2</v>
@@ -12129,7 +12129,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -12137,12 +12137,12 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17">
         <v>0</v>
